--- a/data/trans_orig/Q25B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar</t>
+          <t>Número medio de cigarrillos que fumaban antes de haber dejado de fumar (tasa de respuesta: 96,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,79; 24,95</t>
+          <t>20,59; 24,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,46; 27,31</t>
+          <t>22,71; 27,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,14; 23,83</t>
+          <t>19,04; 23,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,28; 25,86</t>
+          <t>21,14; 25,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,31; 16,23</t>
+          <t>9,08; 16,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,06; 16,92</t>
+          <t>11,0; 16,75</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,92; 16,05</t>
+          <t>10,88; 16,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 12,56</t>
+          <t>8,79; 12,63</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 22,29</t>
+          <t>18,28; 22,36</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,91; 23,77</t>
+          <t>19,89; 23,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,9; 20,86</t>
+          <t>16,83; 20,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,77; 21,79</t>
+          <t>17,69; 21,47</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,31; 25,42</t>
+          <t>21,44; 25,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,98; 24,01</t>
+          <t>19,79; 24,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,33; 24,44</t>
+          <t>20,3; 24,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,59; 22,77</t>
+          <t>19,46; 22,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 12,7</t>
+          <t>9,18; 12,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,55; 16,71</t>
+          <t>11,51; 17,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,2; 14,93</t>
+          <t>11,26; 15,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,13; 14,46</t>
+          <t>11,35; 14,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,07; 21,27</t>
+          <t>18,02; 21,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,07; 21,44</t>
+          <t>17,94; 21,19</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,53; 20,97</t>
+          <t>17,61; 20,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,89; 20,49</t>
+          <t>17,82; 20,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,01; 24,17</t>
+          <t>20,14; 24,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,08; 26,89</t>
+          <t>21,22; 26,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,09; 25,99</t>
+          <t>21,18; 26,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,87; 21,59</t>
+          <t>17,01; 21,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,67; 20,17</t>
+          <t>13,45; 19,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,03; 15,5</t>
+          <t>11,98; 15,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 14,73</t>
+          <t>10,86; 14,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,91; 12,68</t>
+          <t>8,98; 12,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,0; 22,75</t>
+          <t>19,02; 22,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,04; 22,17</t>
+          <t>18,36; 22,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,49</t>
+          <t>17,93; 21,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,72; 18,04</t>
+          <t>14,75; 18,2</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,45; 23,48</t>
+          <t>19,58; 23,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 25,07</t>
+          <t>20,91; 25,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 22,33</t>
+          <t>17,71; 22,5</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 21,16</t>
+          <t>17,7; 21,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,56; 14,82</t>
+          <t>11,57; 14,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 14,71</t>
+          <t>11,48; 14,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,63; 16,35</t>
+          <t>12,68; 16,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,26; 15,09</t>
+          <t>12,14; 14,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,01; 20,02</t>
+          <t>16,99; 19,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,82; 20,93</t>
+          <t>17,89; 21,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 19,28</t>
+          <t>15,94; 19,24</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,82; 18,23</t>
+          <t>15,94; 18,38</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,44</t>
+          <t>21,36; 23,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,11; 24,47</t>
+          <t>22,08; 24,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,54; 22,83</t>
+          <t>20,51; 22,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,74; 21,45</t>
+          <t>19,77; 21,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,56; 13,83</t>
+          <t>11,64; 13,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,62</t>
+          <t>12,44; 14,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,39; 14,4</t>
+          <t>12,41; 14,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,47; 13,11</t>
+          <t>11,39; 13,09</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,72; 20,4</t>
+          <t>18,81; 20,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,22; 21,0</t>
+          <t>19,14; 20,9</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,81; 19,62</t>
+          <t>17,66; 19,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,18</t>
+          <t>17,36; 19,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q25B01-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q25B01-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23,38</t>
+          <t>23,27</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,49</t>
+          <t>10,52</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,51</t>
+          <t>19,44</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>20,59; 24,84</t>
+          <t>20,73; 25,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,71; 27,24</t>
+          <t>22,44; 27,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,04; 23,68</t>
+          <t>19,23; 23,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21,14; 25,8</t>
+          <t>21,41; 25,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,08; 16,29</t>
+          <t>9,35; 16,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 16,75</t>
+          <t>10,98; 16,78</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,88; 16,5</t>
+          <t>10,74; 16,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 12,63</t>
+          <t>8,71; 12,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18,28; 22,36</t>
+          <t>18,31; 22,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19,89; 23,73</t>
+          <t>19,8; 23,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,83; 20,78</t>
+          <t>16,91; 20,68</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,69; 21,47</t>
+          <t>17,71; 21,39</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20,66</t>
+          <t>21,5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12,7</t>
+          <t>12,94</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,29</t>
+          <t>18,55</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>21,44; 25,48</t>
+          <t>21,48; 25,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,79; 24,01</t>
+          <t>20,0; 24,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20,3; 24,76</t>
+          <t>20,04; 24,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19,46; 22,6</t>
+          <t>19,36; 23,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 12,45</t>
+          <t>9,32; 12,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,51; 17,1</t>
+          <t>11,52; 16,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,26; 15,03</t>
+          <t>11,21; 15,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 14,47</t>
+          <t>11,46; 14,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,02; 21,19</t>
+          <t>17,92; 21,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,94; 21,19</t>
+          <t>18,06; 21,35</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17,61; 20,86</t>
+          <t>17,77; 21,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,82; 20,51</t>
+          <t>17,18; 20,22</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19,28</t>
+          <t>18,99</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>10,7</t>
+          <t>10,92</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,33</t>
+          <t>16,29</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,14; 24,18</t>
+          <t>20,17; 24,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,22; 26,92</t>
+          <t>21,41; 26,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,18; 26,14</t>
+          <t>21,07; 25,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17,01; 21,8</t>
+          <t>16,72; 21,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,45; 19,91</t>
+          <t>13,79; 20,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,98; 15,39</t>
+          <t>12,02; 15,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,86; 14,63</t>
+          <t>10,9; 14,53</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,65</t>
+          <t>9,31; 13,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,02; 22,52</t>
+          <t>19,11; 22,54</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,36; 22,27</t>
+          <t>18,3; 22,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 21,62</t>
+          <t>17,65; 21,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 18,2</t>
+          <t>14,64; 17,91</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19,39</t>
+          <t>19,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,54</t>
+          <t>13,48</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,02</t>
+          <t>16,95</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>19,58; 23,52</t>
+          <t>19,45; 23,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 25,23</t>
+          <t>20,92; 25,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,71; 22,5</t>
+          <t>17,65; 22,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 21,16</t>
+          <t>17,86; 21,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,57; 14,89</t>
+          <t>11,52; 14,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 14,96</t>
+          <t>11,37; 14,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 16,6</t>
+          <t>12,59; 16,51</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,14; 14,96</t>
+          <t>12,14; 14,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,99; 19,98</t>
+          <t>17,11; 20,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17,89; 21,08</t>
+          <t>17,99; 21,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15,94; 19,24</t>
+          <t>16,09; 19,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,94; 18,38</t>
+          <t>15,92; 18,19</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,51</t>
+          <t>20,56</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,26</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,17</t>
+          <t>17,63</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>21,36; 23,45</t>
+          <t>21,37; 23,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,08; 24,29</t>
+          <t>22,06; 24,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20,51; 22,81</t>
+          <t>20,49; 22,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,77; 21,55</t>
+          <t>19,54; 21,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,64; 13,87</t>
+          <t>11,5; 13,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,44; 14,52</t>
+          <t>12,42; 14,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,49</t>
+          <t>12,36; 14,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,39; 13,09</t>
+          <t>11,51; 13,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>18,81; 20,59</t>
+          <t>18,73; 20,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19,14; 20,9</t>
+          <t>19,21; 21,02</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,66; 19,54</t>
+          <t>17,85; 19,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,36; 19,12</t>
+          <t>16,91; 18,44</t>
         </is>
       </c>
     </row>
